--- a/docs/revised_shatin/qwen3-next-80b-a3b-instruct/test_grammar_2_['No. 91_～ば〈条件(じょうけん)〉 ']_revised_revised.xlsx
+++ b/docs/revised_shatin/qwen3-next-80b-a3b-instruct/test_grammar_2_['No. 91_～ば〈条件(じょうけん)〉 ']_revised_revised.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F80"/>
+  <dimension ref="A1:F64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -467,12 +467,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい1 お金があれば、(   )。</t>
+          <t>: もんだい11 お金があれば、旅行に(   )。</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>1. 買い物に行きます 2. 友だちと遊びます 3. 家にいます 4. 勉強します</t>
+          <t>1. 行きます 2. 泊まります 3. 走ります 4. 飛びます</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr">
@@ -491,12 +491,12 @@
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい1 時間があれば、(   )。</t>
+          <t>: もんだい12 雨が降れば、ピクニックは(   )。</t>
         </is>
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>1. 手伝いましょう 2. 休みましょう 3. 急ぎましょう 4. 帰りましょう</t>
+          <t>1. 中止になります 2. 中止にします 3. 中止したいです 4. 中止できます</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr">
@@ -515,12 +515,12 @@
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい1 この道をまっすぐ行けば、(   )。</t>
+          <t>: もんだい13 この薬を飲めば、すぐに(   )。</t>
         </is>
       </c>
       <c r="C4" s="1" t="inlineStr">
         <is>
-          <t>1. 駅に着きます 2. 迷います 3. 遠回りします 4. 戻ります</t>
+          <t>1. 治ります 2. 治りません 3. 治ってます 4. 治りそうですね</t>
         </is>
       </c>
       <c r="D4" s="1" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい1 いい天気ならば、(   )。</t>
+          <t>: もんだい14 時間があれば、映画を(   )。</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>1. 外でピクニックをします 2. 家で本を読みます 3. 早く寝ます 4. 映画を見ます</t>
+          <t>1. 見ます 2. 見てます 3. 見ません 4. 見ようと思います</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr">
@@ -563,12 +563,12 @@
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい1 彼が来れば、(   )。</t>
+          <t>: もんだい15 お金があれば、あの車を(   )。</t>
         </is>
       </c>
       <c r="C6" s="1" t="inlineStr">
         <is>
-          <t>1. パーティーを始めます 2. みんな帰ります 3. 終わります 4. 片付けます</t>
+          <t>1. 買います 2. 買いました 3. 買ってます 4. 買わないです</t>
         </is>
       </c>
       <c r="D6" s="1" t="inlineStr">
@@ -587,17 +587,17 @@
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい1 安ければ、(   )。</t>
+          <t>: もんだい10 この薬を飲めば、(   )。</t>
         </is>
       </c>
       <c r="C7" s="1" t="inlineStr">
         <is>
-          <t>1. 買いたいです 2. 売りたいです 3. 借りたいです 4. 捨てたいです</t>
+          <t>1. よくなるかもしれない 2. よくならないかもしれない 3. よくなるつもりだ 4. よくなるはずだ</t>
         </is>
       </c>
       <c r="D7" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E7" s="1" t="inlineStr"/>
@@ -611,17 +611,17 @@
       </c>
       <c r="B8" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい1 早く起きれば、(   )。</t>
+          <t>: もんだい11 時間があれば、(   )。</t>
         </is>
       </c>
       <c r="C8" s="1" t="inlineStr">
         <is>
-          <t>1. 朝ごはんを作れます 2. 遅刻します 3. 寝坊します 4. 忘れ物をします</t>
+          <t>1. 映画を見たい 2. 映画を見よう 3. 映画を見に行きます 4. 映画を見てもいい</t>
         </is>
       </c>
       <c r="D8" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E8" s="1" t="inlineStr"/>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい1 日本語が上手になれば、(   )。</t>
+          <t>: もんだい12 家に帰れば、(   )。</t>
         </is>
       </c>
       <c r="C9" s="1" t="inlineStr">
         <is>
-          <t>1. 日本で働きたいです 2. 日本から帰ります 3. 日本へ行きません 4. 日本語をやめます</t>
+          <t>1. リラックスできる 2. リラックスしなければならない 3. リラックスしていた 4. リラックスします</t>
         </is>
       </c>
       <c r="D9" s="1" t="inlineStr">
@@ -659,17 +659,17 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい1 勉強すれば、(   )。</t>
+          <t>: もんだい13 彼が来れば、(   )。</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>1. テストに合格できます 2. テストに落ちます 3. テストを忘れます 4. テストをしません</t>
+          <t>1. パーティーが始める 2. パーティーを始める 3. パーティーが始まる 4. パーティーを始まる</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E10" s="1" t="inlineStr"/>
@@ -683,12 +683,12 @@
       </c>
       <c r="B11" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい2 雨が 降れば 試合は 中止に (   )。</t>
+          <t>: もんだい20 運動すれば、健康が(   )。</t>
         </is>
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>1. なる 2. する 3. いる 4. ある</t>
+          <t>1. よくなります 2. よいです 3. よくないです 4. よくしてます</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr">
@@ -702,22 +702,22 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Q11</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい2 時間が あれば 本を (   )。</t>
+          <t>: もんだい27 もしお金があれば、新しいスマホを(   )。\n1. 買います 2. 買いたいです 3. 買おうと思います 4. 買うことにしました \nAnswer: 3 Q2: もんだい22 もし雨が降れば、ピクニックは(   )。</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>1. 読む 2. 書く 3. 見る 4. 作る</t>
+          <t>1. 中止にします 2. 中止になります 3. 中止したいです 4. 中止しました</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E12" s="1" t="inlineStr"/>
@@ -726,22 +726,22 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>Q12</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="B13" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい2 お金を ためれば 新しい パソコンを (   )。</t>
+          <t>: もんだい23 彼が来れば、映画を一緒に(   )。</t>
         </is>
       </c>
       <c r="C13" s="1" t="inlineStr">
         <is>
-          <t>1. 買う 2. 売る 3. 借りる 4. 使う</t>
+          <t>1. 見ましょう 2. 見たかった 3. 見たいです 4. 見ます</t>
         </is>
       </c>
       <c r="D13" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E13" s="1" t="inlineStr"/>
@@ -750,17 +750,17 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Q13</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="B14" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい2 早く 寝れば 朝 元気に (   )。</t>
+          <t>: もんだい24 時間があれば、あなたに手紙を(   )。</t>
         </is>
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>1. 起きる 2. 寝る 3. 食べる 4. 行く</t>
+          <t>1. 書きます 2. 書くことにしました 3. 書きたいです 4. 書こうと思います</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr">
@@ -774,17 +774,17 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>Q14</t>
+          <t>Q5</t>
         </is>
       </c>
       <c r="B15" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい2 仕事が 終われば 友達と (   )。</t>
+          <t>: もんだい25 もし彼女が来れば、一緒に(   )。</t>
         </is>
       </c>
       <c r="C15" s="1" t="inlineStr">
         <is>
-          <t>1. 遊ぶ 2. 学ぶ 3. 泳ぐ 4. 働く</t>
+          <t>1. 夕食を食べます 2. 夕食を食べたかった 3. 夕食を食べよう 4. 夕食を食べる</t>
         </is>
       </c>
       <c r="D15" s="1" t="inlineStr">
@@ -798,17 +798,17 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Q15</t>
+          <t>Q6</t>
         </is>
       </c>
       <c r="B16" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい2 天気が 良ければ ピクニックに (   )。</t>
+          <t>: もんだい26 彼女が手伝えば、もっと早く(   )。</t>
         </is>
       </c>
       <c r="C16" s="1" t="inlineStr">
         <is>
-          <t>1. 行く 2. 帰る 3. 来る 4. 戻る</t>
+          <t>1. 終わります 2. 終わらせたかった 3. 終わらせよう 4. 終わらせる</t>
         </is>
       </c>
       <c r="D16" s="1" t="inlineStr">
@@ -822,17 +822,17 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>Q16</t>
+          <t>Q7</t>
         </is>
       </c>
       <c r="B17" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい2 暇が あれば 映画を (   )。</t>
+          <t>: もんだい27 もしお金があれば、新しいスマホを(   )。</t>
         </is>
       </c>
       <c r="C17" s="1" t="inlineStr">
         <is>
-          <t>1. 見る 2. 聞く 3. 話す 4. 描く</t>
+          <t>1. 買います 2. 買いたいです 3. 買おうと思います 4. 買うことにしました</t>
         </is>
       </c>
       <c r="D17" s="1" t="inlineStr">
@@ -846,22 +846,22 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>Q17</t>
+          <t>Q8</t>
         </is>
       </c>
       <c r="B18" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい2 時間が あれば、手伝いに (   )。</t>
+          <t>: もんだい28 もっと練習すれば、試合に(   )。</t>
         </is>
       </c>
       <c r="C18" s="1" t="inlineStr">
         <is>
-          <t>1. 行く 2. 寝る 3. 立つ 4. 走る</t>
+          <t>1. 勝ちたがる 2. 勝てる 3. 勝ちたい 4. 勝ちそうだ</t>
         </is>
       </c>
       <c r="D18" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E18" s="1" t="inlineStr"/>
@@ -870,17 +870,17 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>Q18</t>
+          <t>Q9</t>
         </is>
       </c>
       <c r="B19" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい2 勉強すれば、試験に (   )。</t>
+          <t>: もんだい29 これをやれば、すぐに終わると(   )。</t>
         </is>
       </c>
       <c r="C19" s="1" t="inlineStr">
         <is>
-          <t>1. 合格する 2. 失敗する 3. 落ちる 4. 終わる</t>
+          <t>1. 思います 2. 思っている 3. 思いたい 4. 思った</t>
         </is>
       </c>
       <c r="D19" s="1" t="inlineStr">
@@ -894,22 +894,22 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>Q19</t>
+          <t>Q10</t>
         </is>
       </c>
       <c r="B20" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい2 お金が あれば、旅行に (   )。</t>
+          <t>: もんだい30 この本は面白いが、あの本は(   )面白くない。</t>
         </is>
       </c>
       <c r="C20" s="1" t="inlineStr">
         <is>
-          <t>1. 行く 2. 泊まる 3. 走る 4. 飛ぶ</t>
+          <t>1. とても 2. なら 3. しか 4. ばかり</t>
         </is>
       </c>
       <c r="D20" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E20" s="1" t="inlineStr"/>
@@ -918,22 +918,22 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>Q20</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="B21" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい3 雨が降れば、試合は(   )。</t>
+          <t>: もんだい31 この道をまっすぐ行けば、駅に着きますよ。\n1. なら 2. ば 3. ほど 4. から \nAnswer: 2 Q2: もんだい32 雨が降らなければ、ピクニックに行きます。</t>
         </is>
       </c>
       <c r="C21" s="1" t="inlineStr">
         <is>
-          <t>1. 中止だ 2. 中止にする 3. 中止で 4. 中止になる</t>
+          <t>1. ほど 2. ば 3. から 4. まで</t>
         </is>
       </c>
       <c r="D21" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E21" s="1" t="inlineStr"/>
@@ -942,22 +942,22 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>Q21</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="B22" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい3 この薬を飲めば、すぐに(   )。</t>
+          <t>: もんだい33 宿題を終わらせれば、遊びに行ってもいいです。</t>
         </is>
       </c>
       <c r="C22" s="1" t="inlineStr">
         <is>
-          <t>1. 治る 2. 治らない 3. 治って 4. 治りそう</t>
+          <t>1. から 2. ば 3. ほど 4. だけ</t>
         </is>
       </c>
       <c r="D22" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E22" s="1" t="inlineStr"/>
@@ -966,22 +966,22 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>Q22</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="B23" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい3 時間があれば、映画を(   )。</t>
+          <t>: もんだい34 この映画は怖いが、あの映画は(   )怖くない。</t>
         </is>
       </c>
       <c r="C23" s="1" t="inlineStr">
         <is>
-          <t>1. 見る 2. 見て 3. 見ます 4. 見ない</t>
+          <t>1. ほど 2. から 3. なら 4. まで</t>
         </is>
       </c>
       <c r="D23" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E23" s="1" t="inlineStr"/>
@@ -990,22 +990,22 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Q23</t>
+          <t>Q5</t>
         </is>
       </c>
       <c r="B24" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい3 お金があれば、あの車を(   )。</t>
+          <t>: もんだい35 たくさん練習すれば、上手になります。</t>
         </is>
       </c>
       <c r="C24" s="1" t="inlineStr">
         <is>
-          <t>1. 買う 2. 買いました 3. 買って 4. 買わない</t>
+          <t>1. なら 2. ば 3. ほど 4. から</t>
         </is>
       </c>
       <c r="D24" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E24" s="1" t="inlineStr"/>
@@ -1014,17 +1014,17 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>Q24</t>
+          <t>Q6</t>
         </is>
       </c>
       <c r="B25" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい3 友達が来れば、パーティーがもっと(   )。</t>
+          <t>: もんだい36 お金があれば、旅行に行きたいです。</t>
         </is>
       </c>
       <c r="C25" s="1" t="inlineStr">
         <is>
-          <t>1. 楽しい 2. 楽しむ 3. 楽しんで 4. 楽しくない</t>
+          <t>1. ば 2. から 3. ほど 4. しか</t>
         </is>
       </c>
       <c r="D25" s="1" t="inlineStr">
@@ -1038,17 +1038,17 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>Q25</t>
+          <t>Q7</t>
         </is>
       </c>
       <c r="B26" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい3 天気が良ければ、ピクニックに(   )。</t>
+          <t>: もんだい37 早く寝れば、明日元気になります。</t>
         </is>
       </c>
       <c r="C26" s="1" t="inlineStr">
         <is>
-          <t>1. 行く 2. 行って 3. 行かない 4. 行こう</t>
+          <t>1. ば 2. から 3. ほど 4. だけ</t>
         </is>
       </c>
       <c r="D26" s="1" t="inlineStr">
@@ -1062,17 +1062,17 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>Q26</t>
+          <t>Q8</t>
         </is>
       </c>
       <c r="B27" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい3 もっと勉強すれば、試験に(   )。</t>
+          <t>: もんだい38 彼は賢いが、彼女は(   )賢くない。</t>
         </is>
       </c>
       <c r="C27" s="1" t="inlineStr">
         <is>
-          <t>1. 合格する 2. 合格して 3. 合格しない 4. 合格だ</t>
+          <t>1. ほど 2. ば 3. から 4. まで</t>
         </is>
       </c>
       <c r="D27" s="1" t="inlineStr">
@@ -1086,22 +1086,22 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Q27</t>
+          <t>Q9</t>
         </is>
       </c>
       <c r="B28" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい3 静かにすれば、赤ちゃんが(   )。</t>
+          <t>: もんだい39 勉強すればするほど、試験が簡単になります。</t>
         </is>
       </c>
       <c r="C28" s="1" t="inlineStr">
         <is>
-          <t>1. 眠る 2. 眠って 3. 眠らない 4. 眠い</t>
+          <t>1. なら 2. ば 3. ほど 4. から</t>
         </is>
       </c>
       <c r="D28" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E28" s="1" t="inlineStr"/>
@@ -1110,17 +1110,17 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>Q28</t>
+          <t>Q10</t>
         </is>
       </c>
       <c r="B29" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい3 運動すれば、健康が(   )。</t>
+          <t>: もんだい40 A:「雨が降れば、」 B:「(   )。」</t>
         </is>
       </c>
       <c r="C29" s="1" t="inlineStr">
         <is>
-          <t>1. よくなる 2. よい 3. よくない 4. よくして</t>
+          <t>1. 試合は中止になります 2. 試合が中止です 3. 試合を中止です 4. 試合は中止にします</t>
         </is>
       </c>
       <c r="D29" s="1" t="inlineStr">
@@ -1134,17 +1134,17 @@
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>Q29</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="B30" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい3 早く寝れば、朝早く(   )。</t>
+          <t>: もんだい41 A:「この本、面白ければ、」 B:「(   )。」\n1. 私に貸してもらえますか 2. 私に貸していただけますか 3. 私に貸してくれませんか 4. 私に貸してもいいですか \nAnswer: 3 Q2: もんだい42 A:「時間があれば、」 B:「(   )。」</t>
         </is>
       </c>
       <c r="C30" s="1" t="inlineStr">
         <is>
-          <t>1. 起きられる 2. 起きる 3. 起きない 4. 起きて</t>
+          <t>1. 一緒に行きましょう 2. 一緒に行ってもいいですか 3. 一緒に行ってください 4. 一緒に行ってほしいです</t>
         </is>
       </c>
       <c r="D30" s="1" t="inlineStr">
@@ -1158,22 +1158,22 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>Q30</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="B31" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい4 もし 雨が 降れば、 ピクニックは (   ).</t>
+          <t>: もんだい43 A:「いい天気なら、」 B:「(   )。」</t>
         </is>
       </c>
       <c r="C31" s="1" t="inlineStr">
         <is>
-          <t>1. 中止したい 2. 中止する 3. 中止しよう 4. 中止した</t>
+          <t>1. 山に登りましょう 2. 山に登ります 3. 山に登ってください 4. 山に登りたいです</t>
         </is>
       </c>
       <c r="D31" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E31" s="1" t="inlineStr"/>
@@ -1182,17 +1182,17 @@
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>Q31</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="B32" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい4 彼が 来れば、 映画を 一緒に (   ).</t>
+          <t>: もんだい44 A:「もし暇があれば、」 B:「(   )。」</t>
         </is>
       </c>
       <c r="C32" s="1" t="inlineStr">
         <is>
-          <t>1. 見よう 2. 見たかった 3. 見たい 4. 見る</t>
+          <t>1. 映画を見に行きましょうか 2. 映画を見に行ってください 3. 映画を見に行きますか 4. 映画を見に行ってもいいですか</t>
         </is>
       </c>
       <c r="D32" s="1" t="inlineStr">
@@ -1206,22 +1206,22 @@
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>Q32</t>
+          <t>Q5</t>
         </is>
       </c>
       <c r="B33" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい4 この薬を 飲めば、 すぐに (   ).</t>
+          <t>: もんだい45 A:「風邪を引いたら、」 B:「(   )。」</t>
         </is>
       </c>
       <c r="C33" s="1" t="inlineStr">
         <is>
-          <t>1. よくなりたがる 2. よくなる 3. よくなっている 4. よくなりたい</t>
+          <t>1. 早く寝たほうがいいです 2. 早く寝ますか 3. 早く寝てください 4. 早く寝たらどうですか</t>
         </is>
       </c>
       <c r="D33" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E33" s="1" t="inlineStr"/>
@@ -1230,22 +1230,22 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>Q33</t>
+          <t>Q6</t>
         </is>
       </c>
       <c r="B34" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい4 もし 試験に 合格すれば、 大学に (   ).</t>
+          <t>: もんだい46 A:「道が分からなければ、」 B:「(   )。」</t>
         </is>
       </c>
       <c r="C34" s="1" t="inlineStr">
         <is>
-          <t>1. 行くことにした 2. 行きたかった 3. 行くつもりだ 4. 行こうと思う</t>
+          <t>1. 誰かに聞いてください 2. 誰かに聞きませんか 3. 誰かに聞いてもいいですか 4. 誰かに聞くといいです</t>
         </is>
       </c>
       <c r="D34" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E34" s="1" t="inlineStr"/>
@@ -1254,22 +1254,22 @@
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>Q34</t>
+          <t>Q7</t>
         </is>
       </c>
       <c r="B35" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい4 時間が あれば、 あなたに 手紙を (   ).</t>
+          <t>: もんだい47 A:「お金があれば、」 B:「(   )。」</t>
         </is>
       </c>
       <c r="C35" s="1" t="inlineStr">
         <is>
-          <t>1. 書く 2. 書くことにした 3. 書きたい 4. 書こうと思う</t>
+          <t>1. 新しい車を買います 2. 新しい車を買いますか 3. 新しい車を買ってください 4. 新しい車を買ったらいいです</t>
         </is>
       </c>
       <c r="D35" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E35" s="1" t="inlineStr"/>
@@ -1278,22 +1278,22 @@
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>Q35</t>
+          <t>Q8</t>
         </is>
       </c>
       <c r="B36" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい4 もし 彼女が 来れば、 一緒に (   ).</t>
+          <t>: もんだい48 A:「疲れたら、」 B:「(   )。」</t>
         </is>
       </c>
       <c r="C36" s="1" t="inlineStr">
         <is>
-          <t>1. 夕食を 食べたい 2. 夕食を 食べたかった 3. 夕食を 食べよう 4. 夕食を 食べる</t>
+          <t>1. 休んだほうがいいです 2. 休んでください 3. 休みましょう 4. 休んでもいいですか</t>
         </is>
       </c>
       <c r="D36" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E36" s="1" t="inlineStr"/>
@@ -1302,22 +1302,22 @@
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>Q36</t>
+          <t>Q9</t>
         </is>
       </c>
       <c r="B37" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい4 彼女が 手伝えば、 もっと 早く (   ).</t>
+          <t>: もんだい49 A:「彼が来れば、」 B:「(   )。」</t>
         </is>
       </c>
       <c r="C37" s="1" t="inlineStr">
         <is>
-          <t>1. 終わらせたかった 2. 終わらせたい 3. 終わらせよう 4. 終わらせる</t>
+          <t>1. パーティーを始めます 2. パーティーを始めましょう 3. パーティーを始めてください 4. パーティーを始めてもいいですか</t>
         </is>
       </c>
       <c r="D37" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E37" s="1" t="inlineStr"/>
@@ -1326,17 +1326,17 @@
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>Q37</t>
+          <t>Q10</t>
         </is>
       </c>
       <c r="B38" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい4 もし お金が あれば、 新しいスマホを (   ).</t>
+          <t>: もんだい50 雨が降れば、ピクニックは(   )。</t>
         </is>
       </c>
       <c r="C38" s="1" t="inlineStr">
         <is>
-          <t>1. 買いたい 2. 買う 3. 買おう 4. 買うことにした</t>
+          <t>1. 中止になります 2. 中止にします 3. 中止したいです 4. 中止できます</t>
         </is>
       </c>
       <c r="D38" s="1" t="inlineStr">
@@ -1350,22 +1350,22 @@
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>Q38</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="B39" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい4 もっと 練習すれば、 試合に (   )。</t>
+          <t>: もんだい51 あの映画は面白ければ、(   )。\n1. 見ることになる 2. 見たくなる 3. 見なければならない 4. 見よう \nAnswer: 2 Q2: もんだい52 勉強すれば、テストに(   )。</t>
         </is>
       </c>
       <c r="C39" s="1" t="inlineStr">
         <is>
-          <t>1. 勝ちたがる 2. 勝てる 3. 勝ちたい 4. 勝ちそうだ</t>
+          <t>1. 合格できます 2. 合格します 3. 合格しません 4. 合格になりません</t>
         </is>
       </c>
       <c r="D39" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E39" s="1" t="inlineStr"/>
@@ -1374,22 +1374,22 @@
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>Q39</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="B40" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい4 これを やれば、 すぐに 終わると (   ).</t>
+          <t>: もんだい53 このボタンを押せば、(   )。</t>
         </is>
       </c>
       <c r="C40" s="1" t="inlineStr">
         <is>
-          <t>1. 思った 2. 思っている 3. 思いたい 4. 思う</t>
+          <t>1. ドアが開ける 2. ドアが開く 3. ドアを開ける 4. ドアを開かない</t>
         </is>
       </c>
       <c r="D40" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E40" s="1" t="inlineStr"/>
@@ -1398,17 +1398,17 @@
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>Q40</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="B41" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい5 この本は面白いが、あの本 (   ) 面白くない。</t>
+          <t>: もんだい54 この薬を飲めば、(   )。</t>
         </is>
       </c>
       <c r="C41" s="1" t="inlineStr">
         <is>
-          <t>1. ほど 2. なら 3. しか 4. ばかり</t>
+          <t>1. よくなるかもしれません 2. よくならないかもしれません 3. よくなることにした 4. よくなるつもりだ</t>
         </is>
       </c>
       <c r="D41" s="1" t="inlineStr">
@@ -1422,22 +1422,22 @@
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>Q41</t>
+          <t>Q5</t>
         </is>
       </c>
       <c r="B42" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい5 この道をまっすぐ行け (   ) 駅に着きますよ。</t>
+          <t>: もんだい55 時間があれば、(   )。</t>
         </is>
       </c>
       <c r="C42" s="1" t="inlineStr">
         <is>
-          <t>1. なら 2. ば 3. ほど 4. から</t>
+          <t>1. 映画を見たい 2. 映画を見よう 3. 映画を見ようと思う 4. 映画を見てもいい</t>
         </is>
       </c>
       <c r="D42" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E42" s="1" t="inlineStr"/>
@@ -1446,22 +1446,22 @@
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>Q42</t>
+          <t>Q6</t>
         </is>
       </c>
       <c r="B43" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい5 雨が降らなけれ (   ) ピクニックに行きます。</t>
+          <t>: もんだい56 家に帰れば、(   )。</t>
         </is>
       </c>
       <c r="C43" s="1" t="inlineStr">
         <is>
-          <t>1. ほど 2. ば 3. から 4. まで</t>
+          <t>1. リラックスできます 2. リラックスしなければならない 3. リラックスしています 4. リラックスしたい</t>
         </is>
       </c>
       <c r="D43" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E43" s="1" t="inlineStr"/>
@@ -1470,22 +1470,22 @@
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>Q43</t>
+          <t>Q7</t>
         </is>
       </c>
       <c r="B44" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい5 宿題を終わらせれ (   ) 遊びに行ってもいいです。</t>
+          <t>: もんだい57 お金があれば、(   )。</t>
         </is>
       </c>
       <c r="C44" s="1" t="inlineStr">
         <is>
-          <t>1. から 2. ば 3. ほど 4. だけ</t>
+          <t>1. 旅行に行こう 2. 旅行に行かない 3. 旅行に行くことになった 4. 旅行に行った</t>
         </is>
       </c>
       <c r="D44" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E44" s="1" t="inlineStr"/>
@@ -1494,17 +1494,17 @@
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>Q44</t>
+          <t>Q8</t>
         </is>
       </c>
       <c r="B45" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい5 この映画は怖いが、あの映画 (   ) 怖くない。</t>
+          <t>: もんだい58 この本を読めば、(   )。</t>
         </is>
       </c>
       <c r="C45" s="1" t="inlineStr">
         <is>
-          <t>1. ほど 2. から 3. なら 4. まで</t>
+          <t>1. 話がわかります 2. 話をわかります 3. 話がわかりません 4. 話をわかりません</t>
         </is>
       </c>
       <c r="D45" s="1" t="inlineStr">
@@ -1518,22 +1518,22 @@
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>Q45</t>
+          <t>Q9</t>
         </is>
       </c>
       <c r="B46" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい5 たくさん練習すれ (   ) 上手になります。</t>
+          <t>: もんだい59 その子供は、大人のよう(   )賢い。</t>
         </is>
       </c>
       <c r="C46" s="1" t="inlineStr">
         <is>
-          <t>1. なら 2. ば 3. ほど 4. から</t>
+          <t>1. に 2. で 3. な 4. と</t>
         </is>
       </c>
       <c r="D46" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E46" s="1" t="inlineStr"/>
@@ -1542,22 +1542,22 @@
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>Q46</t>
+          <t>Q10</t>
         </is>
       </c>
       <c r="B47" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい5 お金があれ (   ) 旅行に行きたいです。</t>
+          <t>: もんだい60 彼女が笑えば、太陽のよう(   )明るくなる。</t>
         </is>
       </c>
       <c r="C47" s="1" t="inlineStr">
         <is>
-          <t>1. ば 2. から 3. ほど 4. しか</t>
+          <t>1. に 2. で 3. な 4. と</t>
         </is>
       </c>
       <c r="D47" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E47" s="1" t="inlineStr"/>
@@ -1566,17 +1566,17 @@
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>Q47</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="B48" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい5 早く寝れ (   ) 明日元気になります。</t>
+          <t>: もんだい61 もし疲れれば、猫のよう(   )眠ることができる。\n1. に 2. で 3. な 4. と \nAnswer: 1 Q2: もんだい6 A:「疲れたら、」 B:「(   )。」</t>
         </is>
       </c>
       <c r="C48" s="1" t="inlineStr">
         <is>
-          <t>1. ば 2. から 3. ほど 4. だけ</t>
+          <t>1. 休んだほうがいいです 2. 休んでください 3. 休みましょう 4. 休んでもいいですか</t>
         </is>
       </c>
       <c r="D48" s="1" t="inlineStr">
@@ -1590,22 +1590,22 @@
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>Q48</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="B49" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい5 彼は賢いが、彼女 (   ) 賢くない。</t>
+          <t>: もんだい63 彼女が手伝えば、仕事がまるで魔法のよう(   )早く終わる。</t>
         </is>
       </c>
       <c r="C49" s="1" t="inlineStr">
         <is>
-          <t>1. ほど 2. ば 3. から 4. まで</t>
+          <t>1. に 2. で 3. な 4. と</t>
         </is>
       </c>
       <c r="D49" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E49" s="1" t="inlineStr"/>
@@ -1614,22 +1614,22 @@
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>Q49</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="B50" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい5 勉強すれ (   ) するほど、試験が簡単になります。</t>
+          <t>: もんだい64 あの映画を見れば、夢のよう(   )感じる。</t>
         </is>
       </c>
       <c r="C50" s="1" t="inlineStr">
         <is>
-          <t>1. なら 2. ば 3. ほど 4. から</t>
+          <t>1. に 2. で 3. な 4. と</t>
         </is>
       </c>
       <c r="D50" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E50" s="1" t="inlineStr"/>
@@ -1638,17 +1638,17 @@
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>Q50</t>
+          <t>Q5</t>
         </is>
       </c>
       <c r="B51" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい6 A:「雨が降れば、」 B:「(   )。 」</t>
+          <t>: もんだい65 彼が説明すれば、子供でもわかるよう(   )になる。</t>
         </is>
       </c>
       <c r="C51" s="1" t="inlineStr">
         <is>
-          <t>1. 試合は中止です 2. 試合が中止です 3. 試合を中止です 4. 試合は中止にします</t>
+          <t>1. に 2. で 3. な 4. と</t>
         </is>
       </c>
       <c r="D51" s="1" t="inlineStr">
@@ -1662,22 +1662,22 @@
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>Q51</t>
+          <t>Q6</t>
         </is>
       </c>
       <c r="B52" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい6 A:「この本、面白ければ、」 B:「(   )。 」</t>
+          <t>: もんだい66 彼が来れば、(   )。\n1. パーティーが始める 2. パーティーを始める 3. パーティーが始まる 4. パーティーを始まる \nAnswer: 3 Q7: もんだい67 彼が来れば、すべてがまるで夢のよう(   )解決する。\n1. に 2. で 3. な 4. と \nAnswer: 1 Q8: もんだい6 A:「疲れたら、」 B:「(   )。」</t>
         </is>
       </c>
       <c r="C52" s="1" t="inlineStr">
         <is>
-          <t>1. 私に貸してください 2. 私に貸してもいいですか 3. 私に貸してくれませんか 4. 私に貸していただけますか</t>
+          <t>1. 休んだほうがいいです 2. 休んでください 3. 休みましょう 4. 休んでもいいですか</t>
         </is>
       </c>
       <c r="D52" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E52" s="1" t="inlineStr"/>
@@ -1686,17 +1686,17 @@
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>Q52</t>
+          <t>Q9</t>
         </is>
       </c>
       <c r="B53" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい6 A:「時間があれば、」 B:「(   )。 」</t>
+          <t>: もんだい6 A:「彼が来れば、」 B:「(   )。」</t>
         </is>
       </c>
       <c r="C53" s="1" t="inlineStr">
         <is>
-          <t>1. 一緒に行きませんか 2. 一緒に行ってもいいですか 3. 一緒に行ってください 4. 一緒に行ってほしいです</t>
+          <t>1. パーティーを始めます 2. パーティーを始めましょう 3. パーティーを始めてください 4. パーティーを始めてもいいですか</t>
         </is>
       </c>
       <c r="D53" s="1" t="inlineStr">
@@ -1710,17 +1710,17 @@
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>Q53</t>
+          <t>Q10</t>
         </is>
       </c>
       <c r="B54" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい6 A:「いい天気なら、」 B:「(   )。 」</t>
+          <t>: もんだい7 雨が降れば、ピクニックは(   )。</t>
         </is>
       </c>
       <c r="C54" s="1" t="inlineStr">
         <is>
-          <t>1. 山に登りましょう 2. 山に登ります 3. 山に登ってください 4. 山に登りたいです</t>
+          <t>1. 中止になります 2. 中止にします 3. 中止したいです 4. 中止できます</t>
         </is>
       </c>
       <c r="D54" s="1" t="inlineStr">
@@ -1734,17 +1734,17 @@
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>Q54</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="B55" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい6 A:「もし暇があれば、」 B:「(   )。 」</t>
+          <t>: もんだい7 あの映画は面白ければ、(   )。\n1. 見ることになる 2. 見たくなる 3. 見なければならない 4. 見よう \nAnswer: 2 Q2: もんだい7 勉強すれば、テストに(   )。\n1. 合格できる 2. 合格する 3. 合格しない 4. 合格にならない \nAnswer: 1 Q3: もんだい7 あの映画は面白ければ、(   )。\n1. 見ることになる 2. 見たくなる 3. 見なければならない 4. 見ます \nAnswer: 2 Q4: もんだい7 この薬を飲めば、(   )。\n1. よくなるかもしれない 2. よくならないかもしれない 3. よくなることにした 4. よくなるつもりだ \nAnswer: 1 Q5: もんだい7 時間があれば、(   )。\n1. 映画を見たい 2. 映画を見よう 3. 映画を見ようと思います 4. 映画を見てもいい \nAnswer: 3 Q6: もんだい7 家に帰れば、(   )。</t>
         </is>
       </c>
       <c r="C55" s="1" t="inlineStr">
         <is>
-          <t>1. 映画を見に行きましょうか 2. 映画を見に行ってください 3. 映画を見に行きますか 4. 映画を見に行ってもいいですか</t>
+          <t>1. リラックスできる 2. リラックスしなければならない 3. リラックスしている 4. リラックスしたい</t>
         </is>
       </c>
       <c r="D55" s="1" t="inlineStr">
@@ -1758,22 +1758,22 @@
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>Q55</t>
+          <t>Q7</t>
         </is>
       </c>
       <c r="B56" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい6 A:「風邪を引いたら、」 B:「(   )。 」</t>
+          <t>: もんだい7 天気が良ければ、ピクニックに(   )。\n1. 行きます 2. 帰ります 3. 来ます 4. 戻ります \nAnswer: 1 Q8: もんだい7 彼が来れば、(   )。</t>
         </is>
       </c>
       <c r="C56" s="1" t="inlineStr">
         <is>
-          <t>1. 早く寝たほうがいいです 2. 早く寝ますか 3. 早く寝てください 4. 早く寝たらどうですか</t>
+          <t>1. パーティーが始める 2. パーティーを始める 3. パーティーが始まる 4. パーティーを始まる</t>
         </is>
       </c>
       <c r="D56" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E56" s="1" t="inlineStr"/>
@@ -1782,17 +1782,17 @@
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>Q56</t>
+          <t>Q9</t>
         </is>
       </c>
       <c r="B57" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい6 A:「道が分からなければ、」 B:「(   )。 」</t>
+          <t>: もんだい7 この本を読めば、(   )。</t>
         </is>
       </c>
       <c r="C57" s="1" t="inlineStr">
         <is>
-          <t>1. 誰かに聞いてください 2. 誰かに聞きませんか 3. 誰かに聞いてもいいですか 4. 誰かに聞くといいです</t>
+          <t>1. 話がわかる 2. 話をわかる 3. 話がわからない 4. 話をわからない</t>
         </is>
       </c>
       <c r="D57" s="1" t="inlineStr">
@@ -1806,17 +1806,17 @@
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>Q57</t>
+          <t>Q10</t>
         </is>
       </c>
       <c r="B58" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい6 A:「お金があれば、」 B:「(   )。 」</t>
+          <t>: もんだい8 雨が降れば、道が(   )なる。</t>
         </is>
       </c>
       <c r="C58" s="1" t="inlineStr">
         <is>
-          <t>1. 新しい車を買いたいです 2. 新しい車を買いますか 3. 新しい車を買ってください 4. 新しい車を買ったらいいです</t>
+          <t>1. 滑りやす 2. 滑るように 3. 滑りほど 4. 滑りらしく</t>
         </is>
       </c>
       <c r="D58" s="1" t="inlineStr">
@@ -1830,22 +1830,22 @@
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>Q58</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="B59" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい6 A:「疲れたら、」 B:「(   )。 」</t>
+          <t>: もんだい8 その子供は、大人のよう(   )賢い。\n1. に 2. で 3. な 4. と \nAnswer: 1 Q2: もんだい8 彼女が笑えば、太陽のよう(   )明るくなる。</t>
         </is>
       </c>
       <c r="C59" s="1" t="inlineStr">
         <is>
-          <t>1. 休んだほうがいいです 2. 休んでください 3. 休みましょう 4. 休んでもいいですか</t>
+          <t>1. に 2. で 3. な 4. と</t>
         </is>
       </c>
       <c r="D59" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E59" s="1" t="inlineStr"/>
@@ -1854,22 +1854,22 @@
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>Q59</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="B60" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい6 A:「彼が来れば、」 B:「(   )。 」</t>
+          <t>: もんだい8 もし疲れれば、猫のよう(   )眠ることができる。</t>
         </is>
       </c>
       <c r="C60" s="1" t="inlineStr">
         <is>
-          <t>1. パーティーを始めます 2. パーティーを始めましょう 3. パーティーを始めてください 4. パーティーを始めてもいいですか</t>
+          <t>1. に 2. で 3. な 4. と</t>
         </is>
       </c>
       <c r="D60" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E60" s="1" t="inlineStr"/>
@@ -1878,17 +1878,17 @@
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>Q60</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="B61" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい7 雨が降れば、ピクニックは(   )。</t>
+          <t>: もんだい8 勉強すれば、テストに(   )。</t>
         </is>
       </c>
       <c r="C61" s="1" t="inlineStr">
         <is>
-          <t>1. 中止にしよう 2. 中止になる 3. 中止にする 4. 中止できる</t>
+          <t>1. 合格できる 2. 合格する 3. 合格しない 4. 合格できません</t>
         </is>
       </c>
       <c r="D61" s="1" t="inlineStr">
@@ -1902,22 +1902,22 @@
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>Q61</t>
+          <t>Q5</t>
         </is>
       </c>
       <c r="B62" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい7 あの映画は面白ければ、(   )。</t>
+          <t>: もんだい8 この歌を聴けば、昔のことがまるで映画のよう(   )思い出す。\n1. に 2. で 3. な 4. と \nAnswer: 1 Q6: もんだい8 彼女が手伝えば、仕事がまるで魔法のよう(   )早く終わる。</t>
         </is>
       </c>
       <c r="C62" s="1" t="inlineStr">
         <is>
-          <t>1. 見ることになる 2. 見たくなる 3. 見なければならない 4. 見よう</t>
+          <t>1. に 2. で 3. な 4. と</t>
         </is>
       </c>
       <c r="D62" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E62" s="1" t="inlineStr"/>
@@ -1926,22 +1926,22 @@
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>Q62</t>
+          <t>Q7</t>
         </is>
       </c>
       <c r="B63" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい7 勉強すれば、テストに(   )。</t>
+          <t>: もんだい8 あの映画を見れば、夢のよう(   )感じる。</t>
         </is>
       </c>
       <c r="C63" s="1" t="inlineStr">
         <is>
-          <t>1. 合格できる 2. 合格する 3. 合格しない 4. 合格にならない</t>
+          <t>1. に 2. で 3. な 4. と</t>
         </is>
       </c>
       <c r="D63" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E63" s="1" t="inlineStr"/>
@@ -1950,414 +1950,30 @@
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>Q63</t>
+          <t>Q8</t>
         </is>
       </c>
       <c r="B64" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい7 このボタンを押せば、(   )。</t>
+          <t>: もんだい8 暇があれば、映画を(   )。\n1. 見ます 2. 聞きます 3. 話します 4. 描きます \nAnswer: 1 Q9: もんだい8 この薬を飲めば、魔法のよう(   )効く。</t>
         </is>
       </c>
       <c r="C64" s="1" t="inlineStr">
         <is>
-          <t>1. ドアが開ける 2. ドアが開く 3. ドアを開ける 4. ドアを開かない</t>
+          <t>1. に 2. で 3. な 4. と</t>
         </is>
       </c>
       <c r="D64" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E64" s="1" t="inlineStr"/>
       <c r="F64" s="1" t="inlineStr"/>
     </row>
-    <row r="65">
-      <c r="A65" s="1" t="inlineStr">
-        <is>
-          <t>Q64</t>
-        </is>
-      </c>
-      <c r="B65" s="1" t="inlineStr">
-        <is>
-          <t>: もんだい1 : もんだい7 この薬を飲めば、(   )。</t>
-        </is>
-      </c>
-      <c r="C65" s="1" t="inlineStr">
-        <is>
-          <t>1. よくなるかもしれない 2. よくならないかもしれない 3. よくなることにした 4. よくなるつもりだ</t>
-        </is>
-      </c>
-      <c r="D65" s="1" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E65" s="1" t="inlineStr"/>
-      <c r="F65" s="1" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="1" t="inlineStr">
-        <is>
-          <t>Q65</t>
-        </is>
-      </c>
-      <c r="B66" s="1" t="inlineStr">
-        <is>
-          <t>: もんだい1 : もんだい7 時間があれば、(   )。</t>
-        </is>
-      </c>
-      <c r="C66" s="1" t="inlineStr">
-        <is>
-          <t>1. 映画を見たい 2. 映画を見よう 3. 映画を見ようと思う 4. 映画を見てもいい</t>
-        </is>
-      </c>
-      <c r="D66" s="1" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E66" s="1" t="inlineStr"/>
-      <c r="F66" s="1" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="1" t="inlineStr">
-        <is>
-          <t>Q66</t>
-        </is>
-      </c>
-      <c r="B67" s="1" t="inlineStr">
-        <is>
-          <t>: もんだい1 : もんだい7 家に帰れば、(   )。</t>
-        </is>
-      </c>
-      <c r="C67" s="1" t="inlineStr">
-        <is>
-          <t>1. リラックスできる 2. リラックスしなければならない 3. リラックスしている 4. リラックスしたい</t>
-        </is>
-      </c>
-      <c r="D67" s="1" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E67" s="1" t="inlineStr"/>
-      <c r="F67" s="1" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="1" t="inlineStr">
-        <is>
-          <t>Q67</t>
-        </is>
-      </c>
-      <c r="B68" s="1" t="inlineStr">
-        <is>
-          <t>: もんだい1 : もんだい7 お金があれば、(   )。</t>
-        </is>
-      </c>
-      <c r="C68" s="1" t="inlineStr">
-        <is>
-          <t>1. 旅行に行こう 2. 旅行に行かない 3. 旅行に行くことになった 4. 旅行に行った</t>
-        </is>
-      </c>
-      <c r="D68" s="1" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E68" s="1" t="inlineStr"/>
-      <c r="F68" s="1" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="1" t="inlineStr">
-        <is>
-          <t>Q68</t>
-        </is>
-      </c>
-      <c r="B69" s="1" t="inlineStr">
-        <is>
-          <t>: もんだい1 : もんだい7 彼が来れば、(   )。</t>
-        </is>
-      </c>
-      <c r="C69" s="1" t="inlineStr">
-        <is>
-          <t>1. パーティーが始める 2. パーティーを始める 3. パーティーが始まる 4. パーティーを始まる</t>
-        </is>
-      </c>
-      <c r="D69" s="1" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E69" s="1" t="inlineStr"/>
-      <c r="F69" s="1" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="1" t="inlineStr">
-        <is>
-          <t>Q69</t>
-        </is>
-      </c>
-      <c r="B70" s="1" t="inlineStr">
-        <is>
-          <t>: もんだい1 : もんだい7 この本を読めば、(   )。</t>
-        </is>
-      </c>
-      <c r="C70" s="1" t="inlineStr">
-        <is>
-          <t>1. 話がわかる 2. 話をわかる 3. 話がわからない 4. 話をわからない</t>
-        </is>
-      </c>
-      <c r="D70" s="1" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E70" s="1" t="inlineStr"/>
-      <c r="F70" s="1" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="1" t="inlineStr">
-        <is>
-          <t>Q70</t>
-        </is>
-      </c>
-      <c r="B71" s="1" t="inlineStr">
-        <is>
-          <t>: もんだい1 : もんだい8 雨が降れば、道が(   )なる。</t>
-        </is>
-      </c>
-      <c r="C71" s="1" t="inlineStr">
-        <is>
-          <t>1. みたいに 2. ように 3. ほど 4. らしく</t>
-        </is>
-      </c>
-      <c r="D71" s="1" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E71" s="1" t="inlineStr"/>
-      <c r="F71" s="1" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="1" t="inlineStr">
-        <is>
-          <t>Q71</t>
-        </is>
-      </c>
-      <c r="B72" s="1" t="inlineStr">
-        <is>
-          <t>: もんだい1 : もんだい8 その子供は、大人の(   )賢い。</t>
-        </is>
-      </c>
-      <c r="C72" s="1" t="inlineStr">
-        <is>
-          <t>1. ように 2. ほどに 3. らしく 4. みたい</t>
-        </is>
-      </c>
-      <c r="D72" s="1" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E72" s="1" t="inlineStr"/>
-      <c r="F72" s="1" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="1" t="inlineStr">
-        <is>
-          <t>Q72</t>
-        </is>
-      </c>
-      <c r="B73" s="1" t="inlineStr">
-        <is>
-          <t>: もんだい1 : もんだい8 彼女が笑えば、太陽の(   )明るくなる。</t>
-        </is>
-      </c>
-      <c r="C73" s="1" t="inlineStr">
-        <is>
-          <t>1. ほどに 2. みたいに 3. ように 4. らしく</t>
-        </is>
-      </c>
-      <c r="D73" s="1" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E73" s="1" t="inlineStr"/>
-      <c r="F73" s="1" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="1" t="inlineStr">
-        <is>
-          <t>Q73</t>
-        </is>
-      </c>
-      <c r="B74" s="1" t="inlineStr">
-        <is>
-          <t>: もんだい1 : もんだい8 もし疲れれば、猫の(   )眠ることができる。</t>
-        </is>
-      </c>
-      <c r="C74" s="1" t="inlineStr">
-        <is>
-          <t>1. ように 2. ほどに 3. みたいに 4. らしく</t>
-        </is>
-      </c>
-      <c r="D74" s="1" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E74" s="1" t="inlineStr"/>
-      <c r="F74" s="1" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="1" t="inlineStr">
-        <is>
-          <t>Q74</t>
-        </is>
-      </c>
-      <c r="B75" s="1" t="inlineStr">
-        <is>
-          <t>: もんだい1 : もんだい8 彼が来れば、すべてが(   )解決する。</t>
-        </is>
-      </c>
-      <c r="C75" s="1" t="inlineStr">
-        <is>
-          <t>1. らしく 2. みたいに 3. ように 4. ほど</t>
-        </is>
-      </c>
-      <c r="D75" s="1" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E75" s="1" t="inlineStr"/>
-      <c r="F75" s="1" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="1" t="inlineStr">
-        <is>
-          <t>Q75</t>
-        </is>
-      </c>
-      <c r="B76" s="1" t="inlineStr">
-        <is>
-          <t>: もんだい1 : もんだい8 この歌を聴けば、昔の(   )思い出す。</t>
-        </is>
-      </c>
-      <c r="C76" s="1" t="inlineStr">
-        <is>
-          <t>1. ほどに 2. みたいに 3. ように 4. らしく</t>
-        </is>
-      </c>
-      <c r="D76" s="1" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E76" s="1" t="inlineStr"/>
-      <c r="F76" s="1" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="1" t="inlineStr">
-        <is>
-          <t>Q76</t>
-        </is>
-      </c>
-      <c r="B77" s="1" t="inlineStr">
-        <is>
-          <t>: もんだい1 : もんだい8 彼女が手伝えば、仕事が(   )早く終わる。</t>
-        </is>
-      </c>
-      <c r="C77" s="1" t="inlineStr">
-        <is>
-          <t>1. ように 2. みたいに 3. ほどに 4. らしく</t>
-        </is>
-      </c>
-      <c r="D77" s="1" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E77" s="1" t="inlineStr"/>
-      <c r="F77" s="1" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="1" t="inlineStr">
-        <is>
-          <t>Q77</t>
-        </is>
-      </c>
-      <c r="B78" s="1" t="inlineStr">
-        <is>
-          <t>: もんだい1 : もんだい8 あの映画を見れば、夢の(   )感じる。</t>
-        </is>
-      </c>
-      <c r="C78" s="1" t="inlineStr">
-        <is>
-          <t>1. ように 2. ほどに 3. らしく 4. みたいに</t>
-        </is>
-      </c>
-      <c r="D78" s="1" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E78" s="1" t="inlineStr"/>
-      <c r="F78" s="1" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="1" t="inlineStr">
-        <is>
-          <t>Q78</t>
-        </is>
-      </c>
-      <c r="B79" s="1" t="inlineStr">
-        <is>
-          <t>: もんだい1 : もんだい8 彼が説明すれば、子供でも(   )わかる。</t>
-        </is>
-      </c>
-      <c r="C79" s="1" t="inlineStr">
-        <is>
-          <t>1. ように 2. ほどに 3. みたいに 4. らしく</t>
-        </is>
-      </c>
-      <c r="D79" s="1" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E79" s="1" t="inlineStr"/>
-      <c r="F79" s="1" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="1" t="inlineStr">
-        <is>
-          <t>Q79</t>
-        </is>
-      </c>
-      <c r="B80" s="1" t="inlineStr">
-        <is>
-          <t>: もんだい1 : もんだい8 この薬を飲めば、魔法の(   )効く。</t>
-        </is>
-      </c>
-      <c r="C80" s="1" t="inlineStr">
-        <is>
-          <t>1. みたいに 2. ように 3. ほどに 4. らしく</t>
-        </is>
-      </c>
-      <c r="D80" s="1" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E80" s="1" t="inlineStr"/>
-      <c r="F80" s="1" t="inlineStr"/>
-    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="E2:E80" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E2:E64" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"High_Q,Low_Q,Drop,Minor changes"</formula1>
     </dataValidation>
   </dataValidations>
